--- a/final_data_pipeline/output/311942_elec_options.xlsx
+++ b/final_data_pipeline/output/311942_elec_options.xlsx
@@ -762,7 +762,7 @@
         <v>64</v>
       </c>
       <c r="AD2">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE2">
         <v>8000</v>
@@ -857,7 +857,7 @@
         <v>64</v>
       </c>
       <c r="AD3">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE3">
         <v>8000</v>
@@ -952,7 +952,7 @@
         <v>64</v>
       </c>
       <c r="AD4">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE4">
         <v>8000</v>
@@ -1047,7 +1047,7 @@
         <v>64</v>
       </c>
       <c r="AD5">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE5">
         <v>8000</v>
@@ -1142,7 +1142,7 @@
         <v>64</v>
       </c>
       <c r="AD6">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE6">
         <v>8000</v>
@@ -1237,7 +1237,7 @@
         <v>64</v>
       </c>
       <c r="AD7">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE7">
         <v>8000</v>
@@ -1332,7 +1332,7 @@
         <v>64</v>
       </c>
       <c r="AD8">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE8">
         <v>8000</v>
@@ -1427,7 +1427,7 @@
         <v>64</v>
       </c>
       <c r="AD9">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE9">
         <v>8000</v>
@@ -1522,7 +1522,7 @@
         <v>64</v>
       </c>
       <c r="AD10">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AE10">
         <v>8000</v>
@@ -1617,7 +1617,7 @@
         <v>64</v>
       </c>
       <c r="AD11">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AE11">
         <v>8000</v>
@@ -1712,7 +1712,7 @@
         <v>64</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE12">
         <v>8000</v>
@@ -1807,7 +1807,7 @@
         <v>64</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE13">
         <v>8000</v>
@@ -2472,7 +2472,7 @@
         <v>64</v>
       </c>
       <c r="AD20">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE20">
         <v>8000</v>
@@ -2567,7 +2567,7 @@
         <v>64</v>
       </c>
       <c r="AD21">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE21">
         <v>8000</v>
@@ -2662,7 +2662,7 @@
         <v>64</v>
       </c>
       <c r="AD22">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE22">
         <v>8000</v>
@@ -2757,7 +2757,7 @@
         <v>64</v>
       </c>
       <c r="AD23">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE23">
         <v>8000</v>
@@ -2852,7 +2852,7 @@
         <v>64</v>
       </c>
       <c r="AD24">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE24">
         <v>8000</v>
@@ -2947,7 +2947,7 @@
         <v>64</v>
       </c>
       <c r="AD25">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE25">
         <v>8000</v>
